--- a/data/Monthly Operating Metrics.xlsx
+++ b/data/Monthly Operating Metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -481,115 +481,229 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="C2">
-        <f>B2*11.63</f>
-        <v/>
-      </c>
-      <c r="F2">
-        <f>E2/11.63</f>
-        <v/>
-      </c>
-      <c r="H2">
-        <f>G2/11.63</f>
-        <v/>
+          <t>Jul '25</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>31129</v>
+      </c>
+      <c r="C2" t="n">
+        <v>361960</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="C3">
-        <f>B3*11.63</f>
-        <v/>
-      </c>
-      <c r="F3">
-        <f>E3/11.63</f>
-        <v/>
-      </c>
-      <c r="H3">
-        <f>G3/11.63</f>
-        <v/>
+          <t>Aug '25</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>28752</v>
+      </c>
+      <c r="C3" t="n">
+        <v>334329</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0149</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="C4">
-        <f>B4*11.63</f>
-        <v/>
-      </c>
-      <c r="F4">
-        <f>E4/11.63</f>
-        <v/>
-      </c>
-      <c r="H4">
-        <f>G4/11.63</f>
-        <v/>
+          <t>Sep '25</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>27093</v>
+      </c>
+      <c r="C4" t="n">
+        <v>315038</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.016</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="C5">
-        <f>B5*11.63</f>
-        <v/>
-      </c>
-      <c r="F5">
-        <f>E5/11.63</f>
-        <v/>
-      </c>
-      <c r="H5">
-        <f>G5/11.63</f>
-        <v/>
+          <t>Oct '25</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>25430</v>
+      </c>
+      <c r="C5" t="n">
+        <v>295694</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0161</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="C6">
-        <f>B6*11.63</f>
-        <v/>
-      </c>
-      <c r="F6">
-        <f>E6/11.63</f>
-        <v/>
-      </c>
-      <c r="H6">
-        <f>G6/11.63</f>
-        <v/>
+          <t>Nov '25</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>21445</v>
+      </c>
+      <c r="C6" t="n">
+        <v>249362</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0173</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="C7">
-        <f>B7*11.63</f>
-        <v/>
-      </c>
-      <c r="F7">
-        <f>E7/11.63</f>
-        <v/>
-      </c>
-      <c r="H7">
-        <f>G7/11.63</f>
-        <v/>
+          <t>Dec '25</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>27757</v>
+      </c>
+      <c r="C7" t="n">
+        <v>322759</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0161</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jan '26</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>25594</v>
+      </c>
+      <c r="C8" t="n">
+        <v>297599</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.017</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Feb '26</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>25419</v>
+      </c>
+      <c r="C9" t="n">
+        <v>295571</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0165</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mar '26</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>28310</v>
+      </c>
+      <c r="C10" t="n">
+        <v>329191</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0159</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Apr '26</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>27992</v>
+      </c>
+      <c r="C11" t="n">
+        <v>325483</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0191</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>May '26</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>29259</v>
+      </c>
+      <c r="C12" t="n">
+        <v>340226</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0182</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Jun '26</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>32093</v>
+      </c>
+      <c r="C13" t="n">
+        <v>373172</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0158</v>
       </c>
     </row>
   </sheetData>
